--- a/data/trans_camb/P15A-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P15A-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 0,34</t>
+          <t>-3,24; 0,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 0,73</t>
+          <t>-2,6; 0,78</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 1,79</t>
+          <t>-2,57; 1,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 3,26</t>
+          <t>-0,54; 3,22</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 2,23</t>
+          <t>-1,23; 2,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 1,89</t>
+          <t>-0,94; 2,08</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 1,28</t>
+          <t>-1,3; 1,29</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 0,89</t>
+          <t>-1,32; 1,24</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 1,07</t>
+          <t>-1,23; 1,22</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-68,54; 19,62</t>
+          <t>-71,37; 16,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-64,4; 33,87</t>
+          <t>-62,37; 36,03</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-60,22; 86,77</t>
+          <t>-62,75; 70,81</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-24,81; 214,51</t>
+          <t>-21,0; 201,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-39,59; 150,81</t>
+          <t>-39,82; 163,66</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-31,89; 124,01</t>
+          <t>-31,08; 149,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-37,35; 60,73</t>
+          <t>-37,58; 60,13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-43,56; 41,49</t>
+          <t>-38,72; 63,38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-36,31; 49,82</t>
+          <t>-36,15; 60,7</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 0,18</t>
+          <t>-3,33; 0,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 0,35</t>
+          <t>-3,18; 0,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,23; -0,5</t>
+          <t>-4,2; -0,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 1,17</t>
+          <t>-1,85; 1,07</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 0,73</t>
+          <t>-2,16; 0,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 1,65</t>
+          <t>-1,72; 1,29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 0,15</t>
+          <t>-2,06; 0,23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 0,06</t>
+          <t>-2,2; 0,16</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,62; -0,1</t>
+          <t>-2,59; 0,02</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-61,73; 6,24</t>
+          <t>-59,68; 14,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-55,66; 10,96</t>
+          <t>-56,59; 19,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-77,75; -14,97</t>
+          <t>-76,3; -14,34</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-50,72; 51,04</t>
+          <t>-47,17; 45,36</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-60,41; 36,83</t>
+          <t>-58,3; 34,41</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-44,75; 73,99</t>
+          <t>-45,69; 56,23</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-47,91; 5,12</t>
+          <t>-46,97; 7,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-50,14; 3,17</t>
+          <t>-49,0; 7,51</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-58,73; -2,59</t>
+          <t>-58,35; -0,93</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 0,77</t>
+          <t>-2,78; 0,94</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,86; -0,35</t>
+          <t>-3,69; -0,34</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,66; -0,3</t>
+          <t>-3,68; -0,14</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 0,95</t>
+          <t>-2,71; 0,92</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,11; -0,86</t>
+          <t>-3,85; -0,51</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 0,32</t>
+          <t>-3,44; 0,42</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 0,38</t>
+          <t>-2,27; 0,35</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,13; -0,79</t>
+          <t>-3,27; -0,81</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,84; -0,37</t>
+          <t>-2,87; -0,42</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-63,96; 34,33</t>
+          <t>-60,39; 41,35</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-78,78; -6,74</t>
+          <t>-78,63; -5,84</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-79,12; -5,92</t>
+          <t>-79,87; -4,46</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-58,89; 40,62</t>
+          <t>-59,63; 43,75</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-83,43; -25,24</t>
+          <t>-82,0; -12,93</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-71,99; 12,38</t>
+          <t>-71,21; 15,48</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-51,7; 16,05</t>
+          <t>-51,07; 13,82</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-75,57; -28,25</t>
+          <t>-74,71; -26,59</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-67,24; -13,59</t>
+          <t>-65,72; -13,54</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 1,7</t>
+          <t>-1,66; 1,77</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 0,88</t>
+          <t>-2,26; 1,01</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,25; -0,18</t>
+          <t>-3,33; -0,34</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 1,29</t>
+          <t>-1,35; 1,29</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 2,49</t>
+          <t>-0,43; 2,6</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 1,16</t>
+          <t>-1,35; 1,11</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 1,13</t>
+          <t>-1,09; 1,04</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 1,26</t>
+          <t>-0,88; 1,38</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 0,06</t>
+          <t>-1,88; -0,0</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-38,5; 61,22</t>
+          <t>-36,57; 64,97</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-50,14; 33,58</t>
+          <t>-52,12; 38,31</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-71,5; -6,19</t>
+          <t>-70,82; -7,69</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-48,78; 79,12</t>
+          <t>-46,32; 76,66</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-12,88; 156,2</t>
+          <t>-17,72; 159,49</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-43,32; 73,46</t>
+          <t>-43,87; 66,52</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-30,38; 47,55</t>
+          <t>-31,18; 46,41</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-27,65; 52,96</t>
+          <t>-24,82; 57,11</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-49,52; 4,17</t>
+          <t>-52,0; -0,1</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,76; -0,02</t>
+          <t>-1,76; 0,02</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,04; -0,33</t>
+          <t>-2,04; -0,25</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,58; -0,74</t>
+          <t>-2,55; -0,7</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 0,8</t>
+          <t>-0,82; 0,76</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 0,52</t>
+          <t>-1,05; 0,4</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 0,68</t>
+          <t>-1,18; 0,4</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 0,13</t>
+          <t>-1,06; 0,19</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,41; -0,17</t>
+          <t>-1,31; -0,11</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,53; -0,32</t>
+          <t>-1,63; -0,36</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-41,63; -0,17</t>
+          <t>-41,18; 0,8</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-47,55; -8,93</t>
+          <t>-47,64; -7,48</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-60,25; -20,85</t>
+          <t>-60,78; -20,66</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-27,75; 33,67</t>
+          <t>-26,77; 32,33</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-33,49; 22,16</t>
+          <t>-33,81; 16,35</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-31,93; 28,88</t>
+          <t>-34,88; 15,43</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-30,55; 5,15</t>
+          <t>-29,33; 6,66</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-38,33; -5,57</t>
+          <t>-35,77; -2,64</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-43,6; -11,16</t>
+          <t>-45,66; -12,64</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P15A-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P15A-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-0,67</t>
+          <t>-0,55</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,53</t>
+          <t>0,47</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-0,07</t>
+          <t>-0,04</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 0,26</t>
+          <t>-3,24; 0,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 0,78</t>
+          <t>-2,73; 0,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 1,51</t>
+          <t>-2,41; 2,11</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 3,22</t>
+          <t>-0,51; 3,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 2,37</t>
+          <t>-1,03; 2,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 2,08</t>
+          <t>-1,2; 1,75</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 1,29</t>
+          <t>-1,21; 1,27</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 1,24</t>
+          <t>-1,46; 1,12</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 1,22</t>
+          <t>-1,29; 1,3</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-20,48%</t>
+          <t>-16,8%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-2,54%</t>
+          <t>-1,47%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-71,37; 16,42</t>
+          <t>-73,34; 14,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-62,37; 36,03</t>
+          <t>-61,8; 38,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-62,75; 70,81</t>
+          <t>-59,02; 97,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-21,0; 201,76</t>
+          <t>-18,02; 205,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-39,82; 163,66</t>
+          <t>-38,48; 157,56</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-31,08; 149,06</t>
+          <t>-35,19; 116,91</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-37,58; 60,13</t>
+          <t>-36,09; 57,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-38,72; 63,38</t>
+          <t>-41,37; 52,1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-36,15; 60,7</t>
+          <t>-36,66; 58,07</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-2,2</t>
+          <t>-1,51</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,24</t>
+          <t>-0,28</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-1,25</t>
+          <t>-0,89</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 0,29</t>
+          <t>-3,53; 0,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 0,63</t>
+          <t>-3,01; 0,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,2; -0,48</t>
+          <t>-3,51; 0,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 1,07</t>
+          <t>-1,96; 1,09</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 0,77</t>
+          <t>-2,4; 0,67</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 1,29</t>
+          <t>-1,72; 1,47</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 0,23</t>
+          <t>-2,21; 0,19</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 0,16</t>
+          <t>-2,16; 0,12</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 0,02</t>
+          <t>-2,04; 0,38</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-49,45%</t>
+          <t>-34,0%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-7,62%</t>
+          <t>-8,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-33,09%</t>
+          <t>-23,62%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-59,68; 14,49</t>
+          <t>-62,81; 8,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-56,59; 19,38</t>
+          <t>-54,44; 17,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-76,3; -14,34</t>
+          <t>-62,99; 12,48</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-47,17; 45,36</t>
+          <t>-52,64; 50,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-58,3; 34,41</t>
+          <t>-60,24; 34,65</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-45,69; 56,23</t>
+          <t>-44,4; 65,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-46,97; 7,87</t>
+          <t>-48,25; 6,35</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-49,0; 7,51</t>
+          <t>-49,07; 5,51</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-58,35; -0,93</t>
+          <t>-47,2; 11,3</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-1,8</t>
+          <t>-1,62</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-1,31</t>
+          <t>-0,76</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-1,52</t>
+          <t>-1,19</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 0,94</t>
+          <t>-2,86; 0,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,69; -0,34</t>
+          <t>-3,53; -0,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,68; -0,14</t>
+          <t>-3,41; 0,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 0,92</t>
+          <t>-2,51; 1,04</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,85; -0,51</t>
+          <t>-3,82; -0,73</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 0,42</t>
+          <t>-2,49; 0,82</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 0,35</t>
+          <t>-2,2; 0,47</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,27; -0,81</t>
+          <t>-3,23; -0,97</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,87; -0,42</t>
+          <t>-2,47; -0,0</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-51,4%</t>
+          <t>-46,19%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-37,26%</t>
+          <t>-21,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-43,31%</t>
+          <t>-33,84%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-60,39; 41,35</t>
+          <t>-63,29; 35,28</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-78,63; -5,84</t>
+          <t>-77,96; -1,46</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-79,87; -4,46</t>
+          <t>-72,25; 16,97</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-59,63; 43,75</t>
+          <t>-58,68; 44,9</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-82,0; -12,93</t>
+          <t>-82,83; -25,49</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-71,21; 15,48</t>
+          <t>-53,82; 32,62</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-51,07; 13,82</t>
+          <t>-51,39; 18,88</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-74,71; -26,59</t>
+          <t>-74,23; -29,57</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-65,72; -13,54</t>
+          <t>-57,59; 0,42</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-1,69</t>
+          <t>-1,81</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,08</t>
+          <t>0,07</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,84</t>
+          <t>-0,82</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 1,77</t>
+          <t>-1,7; 1,8</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 1,01</t>
+          <t>-2,34; 1,03</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,33; -0,34</t>
+          <t>-3,32; -0,37</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 1,29</t>
+          <t>-1,21; 1,43</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 2,6</t>
+          <t>-0,39; 2,55</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 1,11</t>
+          <t>-1,24; 1,18</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 1,04</t>
+          <t>-1,03; 1,12</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 1,38</t>
+          <t>-0,86; 1,34</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,88; -0,0</t>
+          <t>-1,84; 0,01</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-47,21%</t>
+          <t>-50,52%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-3,29%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-28,89%</t>
+          <t>-28,31%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-36,57; 64,97</t>
+          <t>-39,49; 65,98</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-52,12; 38,31</t>
+          <t>-51,92; 35,13</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-70,82; -7,69</t>
+          <t>-73,67; -10,68</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-46,32; 76,66</t>
+          <t>-42,71; 92,99</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-17,72; 159,49</t>
+          <t>-17,88; 148,89</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-43,87; 66,52</t>
+          <t>-40,73; 70,48</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-31,18; 46,41</t>
+          <t>-31,17; 48,53</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-24,82; 57,11</t>
+          <t>-25,49; 55,33</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-52,0; -0,1</t>
+          <t>-52,1; 1,52</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-1,65</t>
+          <t>-1,43</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-0,28</t>
+          <t>-0,11</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-0,95</t>
+          <t>-0,76</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 0,02</t>
+          <t>-1,75; -0,02</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,04; -0,25</t>
+          <t>-2,05; -0,26</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,55; -0,7</t>
+          <t>-2,34; -0,52</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 0,76</t>
+          <t>-0,78; 0,85</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 0,4</t>
+          <t>-1,11; 0,46</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 0,4</t>
+          <t>-0,89; 0,61</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 0,19</t>
+          <t>-1,04; 0,16</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,31; -0,11</t>
+          <t>-1,31; -0,18</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,63; -0,36</t>
+          <t>-1,31; -0,19</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-43,88%</t>
+          <t>-37,95%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-10,01%</t>
+          <t>-4,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-29,15%</t>
+          <t>-23,25%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-41,18; 0,8</t>
+          <t>-41,01; -0,92</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-47,64; -7,48</t>
+          <t>-47,86; -7,2</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-60,78; -20,66</t>
+          <t>-55,45; -15,64</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-26,77; 32,33</t>
+          <t>-24,17; 36,3</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-33,81; 16,35</t>
+          <t>-34,57; 19,82</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-34,88; 15,43</t>
+          <t>-27,6; 25,94</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-29,33; 6,66</t>
+          <t>-28,88; 5,63</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-35,77; -2,64</t>
+          <t>-36,59; -5,73</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-45,66; -12,64</t>
+          <t>-36,74; -6,1</t>
         </is>
       </c>
     </row>
